--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:11</t>
+    <t xml:space="preserve">2026-09-09 23:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:06</t>
+    <t xml:space="preserve">2026-09-17 14:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:03</t>
+    <t xml:space="preserve">2026-09-23 12:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:32</t>
+    <t xml:space="preserve">2026-10-02 14:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:07</t>
+    <t xml:space="preserve">2026-10-05 10:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -602,7 +602,7 @@
         <v>2024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1051826.12</v>
+        <v>1051826.13</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
         <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1036939.12</v>
+        <v>1036939.13</v>
       </c>
     </row>
     <row r="6">
@@ -823,7 +823,7 @@
         <v>2024</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>920664.12</v>
+        <v>920664.13</v>
       </c>
     </row>
     <row r="18">
